--- a/member_deposit/2026-10-27_会员沉淀分析.xlsx
+++ b/member_deposit/2026-10-27_会员沉淀分析.xlsx
@@ -452,14 +452,14 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>34764</v>
+        <v>34832</v>
       </c>
       <c r="C2" t="n">
-        <v>34764</v>
+        <v>34832</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>+76</t>
+          <t>+144</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -473,14 +473,14 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>53199</v>
+        <v>53495</v>
       </c>
       <c r="C3" t="n">
-        <v>53199</v>
+        <v>53495</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>+311</t>
+          <t>+607</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -494,14 +494,14 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>78217</v>
+        <v>78421</v>
       </c>
       <c r="C4" t="n">
-        <v>78212</v>
+        <v>78416</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>+231</t>
+          <t>+435</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -515,14 +515,14 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>94379</v>
+        <v>94531</v>
       </c>
       <c r="C5" t="n">
-        <v>94378</v>
+        <v>94530</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>+164</t>
+          <t>+316</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -536,14 +536,14 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>22838</v>
+        <v>22960</v>
       </c>
       <c r="C6" t="n">
-        <v>22838</v>
+        <v>22960</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>+152</t>
+          <t>+274</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -557,14 +557,14 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>25798</v>
+        <v>25892</v>
       </c>
       <c r="C7" t="n">
-        <v>25798</v>
+        <v>25892</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>+99</t>
+          <t>+193</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -578,14 +578,14 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14363</v>
+        <v>14371</v>
       </c>
       <c r="C8" t="n">
-        <v>14362</v>
+        <v>14370</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>+6</t>
+          <t>+14</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -599,14 +599,14 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>14542</v>
+        <v>14574</v>
       </c>
       <c r="C9" t="n">
-        <v>14448</v>
+        <v>14482</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>+12</t>
+          <t>+44</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -620,10 +620,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>338100</v>
+        <v>339076</v>
       </c>
       <c r="C10" t="n">
-        <v>337999</v>
+        <v>338977</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="42">
@@ -1125,7 +1125,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
@@ -1161,7 +1161,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="D4" t="n">
         <v>3</v>
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D5" t="n">
         <v>4</v>
@@ -1197,7 +1197,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="D6" t="n">
         <v>5</v>
@@ -1215,7 +1215,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D7" t="n">
         <v>1</v>
@@ -1233,7 +1233,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="D8" t="n">
         <v>2</v>
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>609</v>
+        <v>615</v>
       </c>
       <c r="D9" t="n">
         <v>3</v>
@@ -1269,7 +1269,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>621</v>
+        <v>626</v>
       </c>
       <c r="D10" t="n">
         <v>4</v>
@@ -1287,7 +1287,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>702</v>
+        <v>706</v>
       </c>
       <c r="D11" t="n">
         <v>5</v>
@@ -1323,7 +1323,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="D13" t="n">
         <v>2</v>
@@ -1341,7 +1341,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>636</v>
+        <v>642</v>
       </c>
       <c r="D14" t="n">
         <v>3</v>
@@ -1377,7 +1377,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>676</v>
+        <v>680</v>
       </c>
       <c r="D16" t="n">
         <v>5</v>
@@ -1395,7 +1395,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
@@ -1431,7 +1431,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="D19" t="n">
         <v>3</v>
@@ -1467,7 +1467,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>797</v>
+        <v>801</v>
       </c>
       <c r="D21" t="n">
         <v>5</v>
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D22" t="n">
         <v>1</v>
@@ -1503,7 +1503,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="D23" t="n">
         <v>2</v>
@@ -1521,7 +1521,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="D24" t="n">
         <v>3</v>
@@ -1539,7 +1539,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="D25" t="n">
         <v>4</v>
@@ -1557,7 +1557,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>782</v>
+        <v>785</v>
       </c>
       <c r="D26" t="n">
         <v>5</v>
@@ -1611,7 +1611,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D29" t="n">
         <v>3</v>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D31" t="n">
         <v>5</v>
